--- a/docs/loja/planilha-demonstracao.xlsx
+++ b/docs/loja/planilha-demonstracao.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
   <si>
     <t xml:space="preserve">ORDEM</t>
   </si>
@@ -37,12 +37,6 @@
     <t xml:space="preserve">VALOR</t>
   </si>
   <si>
-    <t xml:space="preserve">ESTADO DE CONSERVAÇÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SITUAÇÃO DE USO</t>
-  </si>
-  <si>
     <t xml:space="preserve">023101</t>
   </si>
   <si>
@@ -58,12 +52,6 @@
     <t xml:space="preserve">BIBLIOTECA</t>
   </si>
   <si>
-    <t xml:space="preserve">bom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ativo</t>
-  </si>
-  <si>
     <t xml:space="preserve">023102</t>
   </si>
   <si>
@@ -82,9 +70,6 @@
     <t xml:space="preserve">CARLA MENDES</t>
   </si>
   <si>
-    <t xml:space="preserve">inserv.</t>
-  </si>
-  <si>
     <t xml:space="preserve">023104</t>
   </si>
   <si>
@@ -94,9 +79,6 @@
     <t xml:space="preserve">DIEGO LIMA</t>
   </si>
   <si>
-    <t xml:space="preserve">regular</t>
-  </si>
-  <si>
     <t xml:space="preserve">023105</t>
   </si>
   <si>
@@ -104,12 +86,6 @@
   </si>
   <si>
     <t xml:space="preserve">ELISA ROCHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ruim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ocioso</t>
   </si>
   <si>
     <t xml:space="preserve">023106</t>
@@ -584,43 +560,31 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="H2" s="3">
         <v>1890.0</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -628,31 +592,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3" s="3">
         <v>289.9</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -660,31 +618,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H4" s="3">
         <v>649.0</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -692,31 +644,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H5" s="3">
         <v>980.5</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -724,31 +670,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H6" s="3">
         <v>415.0</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -756,31 +696,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H7" s="3">
         <v>238.0</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -788,31 +722,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H8" s="3">
         <v>1320.0</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -820,63 +748,51 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H9" s="3">
         <v>2750.0</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H10" s="3">
         <v>4180.0</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -884,31 +800,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H11" s="3">
         <v>899.0</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -916,31 +826,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H12" s="3">
         <v>1540.0</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -948,31 +852,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H13" s="3">
         <v>310.0</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -980,31 +878,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H14" s="3">
         <v>1890.0</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -1012,31 +904,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="G15" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H15" s="3">
         <v>289.9</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -1044,31 +930,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="G16" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H16" s="3">
         <v>649.0</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -1076,31 +956,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H17" s="3">
         <v>980.5</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -1108,31 +982,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G18" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H18" s="3">
         <v>415.0</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -1140,31 +1008,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H19" s="3">
         <v>238.0</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1172,31 +1034,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H20" s="3">
         <v>1320.0</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -1204,31 +1060,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H21" s="3">
         <v>2750.0</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -1236,31 +1086,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="H22" s="3">
         <v>4180.0</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -1268,31 +1112,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H23" s="3">
         <v>899.0</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -1300,31 +1138,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H24" s="3">
         <v>1540.0</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -1332,31 +1164,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H25" s="3">
         <v>310.0</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -1364,31 +1190,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H26" s="3">
         <v>1890.0</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -1396,31 +1216,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H27" s="3">
         <v>289.9</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -1428,63 +1242,51 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H28" s="3">
         <v>649.0</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G29" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H29" s="3">
         <v>980.5</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -1492,31 +1294,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H30" s="3">
         <v>415.0</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -1524,31 +1320,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H31" s="3">
         <v>238.0</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="32">
@@ -1556,31 +1346,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H32" s="3">
         <v>1320.0</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -1588,31 +1372,25 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H33" s="3">
         <v>2750.0</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="34">
@@ -1620,31 +1398,25 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H34" s="3">
         <v>4180.0</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -1652,31 +1424,25 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H35" s="3">
         <v>899.0</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="36">
@@ -1684,31 +1450,25 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H36" s="3">
         <v>1540.0</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="37">
@@ -1716,31 +1476,25 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H37" s="3">
         <v>310.0</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="38">
@@ -1748,31 +1502,25 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H38" s="3">
         <v>1890.0</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="39">
@@ -1780,31 +1528,25 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H39" s="3">
         <v>289.9</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="40">
@@ -1812,31 +1554,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G40" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H40" s="3">
         <v>649.0</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -1844,31 +1580,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H41" s="3">
         <v>980.5</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -1876,31 +1606,25 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H42" s="3">
         <v>415.0</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="43">
@@ -1908,31 +1632,25 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H43" s="3">
         <v>238.0</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="44">
@@ -1940,31 +1658,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H44" s="3">
         <v>1320.0</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="45">
@@ -1972,31 +1684,25 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H45" s="3">
         <v>2750.0</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="46">
@@ -2004,31 +1710,25 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H46" s="3">
         <v>4180.0</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -2036,31 +1736,25 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H47" s="3">
         <v>899.0</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="48">
@@ -2068,31 +1762,25 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H48" s="3">
         <v>1540.0</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="49">
@@ -2100,31 +1788,25 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H49" s="3">
         <v>310.0</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="50">
@@ -2132,31 +1814,25 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H50" s="3">
         <v>1890.0</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="51">
@@ -2164,31 +1840,25 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G51" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H51" s="3">
         <v>289.9</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="52">
@@ -2196,31 +1866,25 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H52" s="3">
         <v>649.0</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="53">
@@ -2228,31 +1892,25 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H53" s="3">
         <v>980.5</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="54">
@@ -2260,31 +1918,25 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H54" s="3">
         <v>415.0</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="55">
@@ -2292,31 +1944,25 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H55" s="3">
         <v>238.0</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="56">
@@ -2324,31 +1970,25 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H56" s="3">
         <v>1320.0</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -2356,31 +1996,25 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H57" s="3">
         <v>2750.0</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="58">
@@ -2388,31 +2022,25 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H58" s="3">
         <v>4180.0</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="59">
@@ -2420,31 +2048,25 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H59" s="3">
         <v>899.0</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="60">
@@ -2452,31 +2074,25 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H60" s="3">
         <v>1540.0</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="61">
@@ -2484,31 +2100,25 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H61" s="3">
         <v>310.0</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/docs/loja/planilha-demonstracao.xlsx
+++ b/docs/loja/planilha-demonstracao.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="157">
   <si>
     <t xml:space="preserve">ORDEM</t>
   </si>
@@ -37,6 +37,12 @@
     <t xml:space="preserve">VALOR</t>
   </si>
   <si>
+    <t xml:space="preserve">ESTADO DE CONSERVAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-19434</t>
+  </si>
+  <si>
     <t xml:space="preserve">023101</t>
   </si>
   <si>
@@ -52,6 +58,12 @@
     <t xml:space="preserve">BIBLIOTECA</t>
   </si>
   <si>
+    <t xml:space="preserve">Bom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-19433</t>
+  </si>
+  <si>
     <t xml:space="preserve">023102</t>
   </si>
   <si>
@@ -61,6 +73,9 @@
     <t xml:space="preserve">BRUNO CARVALHO</t>
   </si>
   <si>
+    <t xml:space="preserve">-19432</t>
+  </si>
+  <si>
     <t xml:space="preserve">023103</t>
   </si>
   <si>
@@ -70,6 +85,12 @@
     <t xml:space="preserve">CARLA MENDES</t>
   </si>
   <si>
+    <t xml:space="preserve">Ocioso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-19431</t>
+  </si>
+  <si>
     <t xml:space="preserve">023104</t>
   </si>
   <si>
@@ -79,6 +100,9 @@
     <t xml:space="preserve">DIEGO LIMA</t>
   </si>
   <si>
+    <t xml:space="preserve">-19430</t>
+  </si>
+  <si>
     <t xml:space="preserve">023105</t>
   </si>
   <si>
@@ -88,12 +112,21 @@
     <t xml:space="preserve">ELISA ROCHA</t>
   </si>
   <si>
+    <t xml:space="preserve">Recuperável</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-19429</t>
+  </si>
+  <si>
     <t xml:space="preserve">023106</t>
   </si>
   <si>
     <t xml:space="preserve">QUADRO BRANCO 120 X 90</t>
   </si>
   <si>
+    <t xml:space="preserve">-19428</t>
+  </si>
+  <si>
     <t xml:space="preserve">023107</t>
   </si>
   <si>
@@ -103,187 +136,349 @@
     <t xml:space="preserve">NOBREAK 1500VA</t>
   </si>
   <si>
+    <t xml:space="preserve">Antieconômico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-19427</t>
+  </si>
+  <si>
     <t xml:space="preserve">023108</t>
   </si>
   <si>
     <t xml:space="preserve">PROJETOR MULTIMÍDIA 3500 LUMENS</t>
   </si>
   <si>
+    <t xml:space="preserve">-19426</t>
+  </si>
+  <si>
     <t xml:space="preserve">023109</t>
   </si>
   <si>
     <t xml:space="preserve">MICROCOMPUTADOR DESKTOP</t>
   </si>
   <si>
+    <t xml:space="preserve">-19425</t>
+  </si>
+  <si>
     <t xml:space="preserve">023110</t>
   </si>
   <si>
     <t xml:space="preserve">MONITOR LED 24 POLEGADAS</t>
   </si>
   <si>
+    <t xml:space="preserve">-19424</t>
+  </si>
+  <si>
     <t xml:space="preserve">023111</t>
   </si>
   <si>
     <t xml:space="preserve">IMPRESSORA LASER MONOCROMÁTICA</t>
   </si>
   <si>
+    <t xml:space="preserve">-19423</t>
+  </si>
+  <si>
     <t xml:space="preserve">023112</t>
   </si>
   <si>
     <t xml:space="preserve">ESTABILIZADOR ELETRÔNICO 1000VA</t>
   </si>
   <si>
+    <t xml:space="preserve">-19422</t>
+  </si>
+  <si>
     <t xml:space="preserve">023113</t>
   </si>
   <si>
     <t xml:space="preserve">LAB. INFORMÁTICA 1</t>
   </si>
   <si>
+    <t xml:space="preserve">-19421</t>
+  </si>
+  <si>
     <t xml:space="preserve">023114</t>
   </si>
   <si>
+    <t xml:space="preserve">-19420</t>
+  </si>
+  <si>
     <t xml:space="preserve">023115</t>
   </si>
   <si>
+    <t xml:space="preserve">-19419</t>
+  </si>
+  <si>
     <t xml:space="preserve">023116</t>
   </si>
   <si>
+    <t xml:space="preserve">-19418</t>
+  </si>
+  <si>
     <t xml:space="preserve">023117</t>
   </si>
   <si>
+    <t xml:space="preserve">-19417</t>
+  </si>
+  <si>
     <t xml:space="preserve">023118</t>
   </si>
   <si>
+    <t xml:space="preserve">-19416</t>
+  </si>
+  <si>
     <t xml:space="preserve">023119</t>
   </si>
   <si>
+    <t xml:space="preserve">-19415</t>
+  </si>
+  <si>
     <t xml:space="preserve">023120</t>
   </si>
   <si>
+    <t xml:space="preserve">-19414</t>
+  </si>
+  <si>
     <t xml:space="preserve">023121</t>
   </si>
   <si>
+    <t xml:space="preserve">-19413</t>
+  </si>
+  <si>
     <t xml:space="preserve">023122</t>
   </si>
   <si>
+    <t xml:space="preserve">-19412</t>
+  </si>
+  <si>
     <t xml:space="preserve">023123</t>
   </si>
   <si>
+    <t xml:space="preserve">-19411</t>
+  </si>
+  <si>
     <t xml:space="preserve">023124</t>
   </si>
   <si>
+    <t xml:space="preserve">-19410</t>
+  </si>
+  <si>
     <t xml:space="preserve">023125</t>
   </si>
   <si>
     <t xml:space="preserve">AUDITÓRIO</t>
   </si>
   <si>
+    <t xml:space="preserve">-19409</t>
+  </si>
+  <si>
     <t xml:space="preserve">023126</t>
   </si>
   <si>
+    <t xml:space="preserve">-19408</t>
+  </si>
+  <si>
     <t xml:space="preserve">023127</t>
   </si>
   <si>
+    <t xml:space="preserve">-19407</t>
+  </si>
+  <si>
     <t xml:space="preserve">023128</t>
   </si>
   <si>
+    <t xml:space="preserve">-19406</t>
+  </si>
+  <si>
     <t xml:space="preserve">023129</t>
   </si>
   <si>
+    <t xml:space="preserve">-19405</t>
+  </si>
+  <si>
     <t xml:space="preserve">023130</t>
   </si>
   <si>
+    <t xml:space="preserve">-19404</t>
+  </si>
+  <si>
     <t xml:space="preserve">023131</t>
   </si>
   <si>
+    <t xml:space="preserve">-19403</t>
+  </si>
+  <si>
     <t xml:space="preserve">023132</t>
   </si>
   <si>
+    <t xml:space="preserve">-19402</t>
+  </si>
+  <si>
     <t xml:space="preserve">023133</t>
   </si>
   <si>
+    <t xml:space="preserve">-19401</t>
+  </si>
+  <si>
     <t xml:space="preserve">023134</t>
   </si>
   <si>
+    <t xml:space="preserve">-19400</t>
+  </si>
+  <si>
     <t xml:space="preserve">023135</t>
   </si>
   <si>
+    <t xml:space="preserve">-19399</t>
+  </si>
+  <si>
     <t xml:space="preserve">023136</t>
   </si>
   <si>
+    <t xml:space="preserve">-19398</t>
+  </si>
+  <si>
     <t xml:space="preserve">023137</t>
   </si>
   <si>
     <t xml:space="preserve">COORDENAÇÃO DE CURSO</t>
   </si>
   <si>
+    <t xml:space="preserve">-19397</t>
+  </si>
+  <si>
     <t xml:space="preserve">023138</t>
   </si>
   <si>
+    <t xml:space="preserve">-19396</t>
+  </si>
+  <si>
     <t xml:space="preserve">023139</t>
   </si>
   <si>
+    <t xml:space="preserve">-19395</t>
+  </si>
+  <si>
     <t xml:space="preserve">023140</t>
   </si>
   <si>
+    <t xml:space="preserve">-19394</t>
+  </si>
+  <si>
     <t xml:space="preserve">023141</t>
   </si>
   <si>
+    <t xml:space="preserve">-19393</t>
+  </si>
+  <si>
     <t xml:space="preserve">023142</t>
   </si>
   <si>
+    <t xml:space="preserve">-19392</t>
+  </si>
+  <si>
     <t xml:space="preserve">023143</t>
   </si>
   <si>
+    <t xml:space="preserve">-19391</t>
+  </si>
+  <si>
     <t xml:space="preserve">023144</t>
   </si>
   <si>
+    <t xml:space="preserve">-19390</t>
+  </si>
+  <si>
     <t xml:space="preserve">023145</t>
   </si>
   <si>
+    <t xml:space="preserve">-19389</t>
+  </si>
+  <si>
     <t xml:space="preserve">023146</t>
   </si>
   <si>
+    <t xml:space="preserve">-19388</t>
+  </si>
+  <si>
     <t xml:space="preserve">023147</t>
   </si>
   <si>
+    <t xml:space="preserve">-19387</t>
+  </si>
+  <si>
     <t xml:space="preserve">023148</t>
   </si>
   <si>
+    <t xml:space="preserve">-19386</t>
+  </si>
+  <si>
     <t xml:space="preserve">023149</t>
   </si>
   <si>
     <t xml:space="preserve">SALA DOS PROFESSORES</t>
   </si>
   <si>
+    <t xml:space="preserve">-19385</t>
+  </si>
+  <si>
     <t xml:space="preserve">023150</t>
   </si>
   <si>
+    <t xml:space="preserve">-19384</t>
+  </si>
+  <si>
     <t xml:space="preserve">023151</t>
   </si>
   <si>
+    <t xml:space="preserve">-19383</t>
+  </si>
+  <si>
     <t xml:space="preserve">023152</t>
   </si>
   <si>
+    <t xml:space="preserve">-19382</t>
+  </si>
+  <si>
     <t xml:space="preserve">023153</t>
   </si>
   <si>
+    <t xml:space="preserve">-19381</t>
+  </si>
+  <si>
     <t xml:space="preserve">023154</t>
   </si>
   <si>
+    <t xml:space="preserve">-19380</t>
+  </si>
+  <si>
     <t xml:space="preserve">023155</t>
   </si>
   <si>
+    <t xml:space="preserve">-19379</t>
+  </si>
+  <si>
     <t xml:space="preserve">023156</t>
   </si>
   <si>
+    <t xml:space="preserve">-19378</t>
+  </si>
+  <si>
     <t xml:space="preserve">023157</t>
   </si>
   <si>
+    <t xml:space="preserve">-19377</t>
+  </si>
+  <si>
     <t xml:space="preserve">023158</t>
   </si>
   <si>
+    <t xml:space="preserve">-19376</t>
+  </si>
+  <si>
     <t xml:space="preserve">023159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-19375</t>
   </si>
   <si>
     <t xml:space="preserve">023160</t>
@@ -560,31 +755,37 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H2" s="3">
         <v>1890.0</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -592,25 +793,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="H3" s="3">
         <v>289.9</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -618,25 +822,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H4" s="3">
         <v>649.0</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -644,25 +851,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3">
         <v>980.5</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -670,25 +880,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H6" s="3">
         <v>415.0</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -696,25 +909,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H7" s="3">
         <v>238.0</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -722,25 +938,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H8" s="3">
         <v>1320.0</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +967,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H9" s="3">
         <v>2750.0</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -774,25 +996,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H10" s="3">
         <v>4180.0</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -800,51 +1025,57 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H11" s="3">
         <v>899.0</v>
       </c>
+      <c r="I11" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H12" s="3">
         <v>1540.0</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -852,25 +1083,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H13" s="3">
         <v>310.0</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -878,25 +1112,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H14" s="3">
         <v>1890.0</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15">
@@ -904,51 +1141,57 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H15" s="3">
         <v>289.9</v>
       </c>
+      <c r="I15" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H16" s="3">
         <v>649.0</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -956,25 +1199,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H17" s="3">
         <v>980.5</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -982,25 +1228,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H18" s="3">
         <v>415.0</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -1008,25 +1257,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H19" s="3">
         <v>238.0</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1034,25 +1286,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H20" s="3">
         <v>1320.0</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -1060,25 +1315,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="G21" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H21" s="3">
         <v>2750.0</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1086,25 +1344,28 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H22" s="3">
         <v>4180.0</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -1112,25 +1373,28 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H23" s="3">
         <v>899.0</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -1138,25 +1402,28 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H24" s="3">
         <v>1540.0</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="25">
@@ -1164,25 +1431,28 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H25" s="3">
         <v>310.0</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -1190,25 +1460,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H26" s="3">
         <v>1890.0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -1216,25 +1489,28 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H27" s="3">
         <v>289.9</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -1242,25 +1518,28 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H28" s="3">
         <v>649.0</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="29">
@@ -1268,25 +1547,28 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H29" s="3">
         <v>980.5</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -1294,25 +1576,28 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H30" s="3">
         <v>415.0</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="31">
@@ -1320,25 +1605,28 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H31" s="3">
         <v>238.0</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1346,25 +1634,28 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="G32" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H32" s="3">
         <v>1320.0</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="33">
@@ -1372,25 +1663,28 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H33" s="3">
         <v>2750.0</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -1398,25 +1692,28 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H34" s="3">
         <v>4180.0</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -1424,25 +1721,28 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H35" s="3">
         <v>899.0</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -1450,25 +1750,28 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H36" s="3">
         <v>1540.0</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="37">
@@ -1476,25 +1779,28 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="G37" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H37" s="3">
         <v>310.0</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="38">
@@ -1502,25 +1808,28 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="H38" s="3">
         <v>1890.0</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="39">
@@ -1528,51 +1837,57 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="H39" s="3">
         <v>289.9</v>
       </c>
+      <c r="I39" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="H40" s="3">
         <v>649.0</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="41">
@@ -1580,25 +1895,28 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="H41" s="3">
         <v>980.5</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -1606,25 +1924,28 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G42" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="H42" s="3">
         <v>415.0</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -1632,25 +1953,28 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="H43" s="3">
         <v>238.0</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -1658,25 +1982,28 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="H44" s="3">
         <v>1320.0</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="45">
@@ -1684,25 +2011,28 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="H45" s="3">
         <v>2750.0</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -1710,25 +2040,28 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="H46" s="3">
         <v>4180.0</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="47">
@@ -1736,25 +2069,28 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="H47" s="3">
         <v>899.0</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="48">
@@ -1762,25 +2098,28 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="G48" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="H48" s="3">
         <v>1540.0</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="49">
@@ -1788,25 +2127,28 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="H49" s="3">
         <v>310.0</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -1814,25 +2156,28 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H50" s="3">
         <v>1890.0</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="51">
@@ -1840,25 +2185,28 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H51" s="3">
         <v>289.9</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="52">
@@ -1866,25 +2214,28 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H52" s="3">
         <v>649.0</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="53">
@@ -1892,25 +2243,28 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H53" s="3">
         <v>980.5</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="54">
@@ -1918,25 +2272,28 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H54" s="3">
         <v>415.0</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="55">
@@ -1944,25 +2301,28 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H55" s="3">
         <v>238.0</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="56">
@@ -1970,25 +2330,28 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H56" s="3">
         <v>1320.0</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="57">
@@ -1996,25 +2359,28 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>87</v>
+        <v>148</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H57" s="3">
         <v>2750.0</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="58">
@@ -2022,25 +2388,28 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H58" s="3">
         <v>4180.0</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="59">
@@ -2048,25 +2417,28 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="D59" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="G59" s="1" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H59" s="3">
         <v>899.0</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="60">
@@ -2074,25 +2446,28 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>90</v>
+        <v>153</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H60" s="3">
         <v>1540.0</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="61">
@@ -2100,25 +2475,28 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>91</v>
+        <v>155</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="H61" s="3">
         <v>310.0</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
